--- a/経営管理/02_財務・会計/売上利益管理/初心者向け_売上利益シート.xlsx
+++ b/経営管理/02_財務・会計/売上利益管理/初心者向け_売上利益シート.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,8 +47,25 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <color rgb="0016293F"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <color rgb="001A2433"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -75,8 +92,18 @@
         <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3A5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF3FA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -98,11 +125,45 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="00C8A24B"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D7DEE8"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D7DEE8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D7DEE8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D7DEE8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="00C8A24B"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <right/>
+      <bottom style="medium">
+        <color rgb="00C8A24B"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -133,6 +194,82 @@
     </xf>
     <xf numFmtId="3" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -496,25 +633,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F3A5F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="20.36" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="27.8" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="17.88" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>🔰 かんたん売上利益シート（今年・第8期）</t>
         </is>
       </c>
+      <c r="B1" s="14" t="n"/>
+      <c r="C1" s="14" t="n"/>
+      <c r="D1" s="14" t="n"/>
+      <c r="E1" s="14" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -523,6 +665,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -530,552 +673,623 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>こうもく</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>きんがく</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>かんたんな説明</t>
         </is>
       </c>
+      <c r="D5" s="15" t="n"/>
+      <c r="E5" s="15" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>💰 売上（うりあげ）</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="31" t="inlineStr">
         <is>
           <t>8.8億円</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>お客様から受け取ったお金の合計</t>
         </is>
       </c>
+      <c r="D6" s="31" t="n"/>
+      <c r="E6" s="31" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="32" t="inlineStr">
         <is>
           <t>✨ 利益（りえき）</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>3.8億円</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>売上から費用をひいて、会社に残ったお金</t>
         </is>
       </c>
+      <c r="D7" s="33" t="n"/>
+      <c r="E7" s="33" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>📝 契約の数</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>128件</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>今年これまでに決まった契約の件数</t>
         </is>
       </c>
+      <c r="D8" s="31" t="n"/>
+      <c r="E8" s="31" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>📊 1件あたりの利益</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>約296万円</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>契約1件で平均どれくらい儲かったか</t>
         </is>
       </c>
+      <c r="D9" s="33" t="n"/>
+      <c r="E9" s="33" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>🎯 売上の目標</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="31" t="inlineStr">
         <is>
           <t>21億円</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>今年めざす売上</t>
         </is>
       </c>
+      <c r="D10" s="31" t="n"/>
+      <c r="E10" s="31" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">　→ 達成ぐあい</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>目標までどれくらい進んだか</t>
         </is>
       </c>
+      <c r="D11" s="33" t="n"/>
+      <c r="E11" s="33" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>🎯 利益の目標</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>4.8億円</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>今年めざす利益</t>
         </is>
       </c>
+      <c r="D12" s="31" t="n"/>
+      <c r="E12" s="31" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">　→ 達成ぐあい</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="33" t="inlineStr">
         <is>
           <t>79%</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>目標までどれくらい進んだか（あと少し！）</t>
         </is>
       </c>
+      <c r="D13" s="33" t="n"/>
+      <c r="E13" s="33" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="30" t="n"/>
+      <c r="B14" s="31" t="n"/>
+      <c r="C14" s="18" t="n"/>
+      <c r="D14" s="31" t="n"/>
+      <c r="E14" s="31" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="32" t="n"/>
+      <c r="B15" s="33" t="n"/>
+      <c r="C15" s="21" t="n"/>
+      <c r="D15" s="33" t="n"/>
+      <c r="E15" s="33" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="30" t="inlineStr">
         <is>
           <t>② 月ごとの売上と利益（万円）</t>
         </is>
       </c>
+      <c r="B16" s="31" t="n"/>
+      <c r="C16" s="18" t="n"/>
+      <c r="D16" s="31" t="n"/>
+      <c r="E16" s="31" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="32" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="33" t="inlineStr">
         <is>
           <t>売上（万円）</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>利益（万円）</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="33" t="inlineStr">
         <is>
           <t>契約数</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" s="33" t="inlineStr">
         <is>
           <t>ひとことメモ</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="30" t="inlineStr">
         <is>
           <t>2025年08月</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
+      <c r="B18" s="34" t="n">
         <v>2650</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="23" t="n">
         <v>1995</v>
       </c>
-      <c r="D18" s="7" t="n">
+      <c r="D18" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="E18" s="5" t="inlineStr"/>
+      <c r="E18" s="31" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="32" t="inlineStr">
         <is>
           <t>2025年09月</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n">
+      <c r="B19" s="35" t="n">
         <v>12166</v>
       </c>
-      <c r="C19" s="8" t="n">
+      <c r="C19" s="25" t="n">
         <v>3108</v>
       </c>
-      <c r="D19" s="8" t="n">
+      <c r="D19" s="35" t="n">
         <v>16</v>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="33" t="inlineStr">
         <is>
           <t>好調</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="30" t="inlineStr">
         <is>
           <t>2025年10月</t>
         </is>
       </c>
-      <c r="B20" s="7" t="n">
+      <c r="B20" s="34" t="n">
         <v>8750</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="23" t="n">
         <v>1943</v>
       </c>
-      <c r="D20" s="7" t="n">
+      <c r="D20" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="E20" s="5" t="inlineStr"/>
+      <c r="E20" s="31" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="32" t="inlineStr">
         <is>
           <t>2025年11月</t>
         </is>
       </c>
-      <c r="B21" s="8" t="n">
+      <c r="B21" s="35" t="n">
         <v>5846</v>
       </c>
-      <c r="C21" s="8" t="n">
+      <c r="C21" s="25" t="n">
         <v>3279</v>
       </c>
-      <c r="D21" s="8" t="n">
+      <c r="D21" s="35" t="n">
         <v>11</v>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="33" t="inlineStr">
         <is>
           <t>好調</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="36" t="inlineStr">
         <is>
           <t>2025年12月</t>
         </is>
       </c>
-      <c r="B22" s="10" t="n">
+      <c r="B22" s="37" t="n">
         <v>18180</v>
       </c>
-      <c r="C22" s="10" t="n">
+      <c r="C22" s="28" t="n">
         <v>7955</v>
       </c>
-      <c r="D22" s="10" t="n">
+      <c r="D22" s="37" t="n">
         <v>21</v>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E22" s="38" t="inlineStr">
         <is>
           <t>⭐ いちばん利益が多い月！</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="32" t="inlineStr">
         <is>
           <t>2026年01月</t>
         </is>
       </c>
-      <c r="B23" s="8" t="n">
+      <c r="B23" s="35" t="n">
         <v>6640</v>
       </c>
-      <c r="C23" s="8" t="n">
+      <c r="C23" s="25" t="n">
         <v>2367</v>
       </c>
-      <c r="D23" s="8" t="n">
+      <c r="D23" s="35" t="n">
         <v>9</v>
       </c>
-      <c r="E23" s="6" t="inlineStr"/>
+      <c r="E23" s="33" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="30" t="inlineStr">
         <is>
           <t>2026年02月</t>
         </is>
       </c>
-      <c r="B24" s="7" t="n">
+      <c r="B24" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="23" t="n">
         <v>2994</v>
       </c>
-      <c r="D24" s="7" t="n">
+      <c r="D24" s="34" t="n">
         <v>11</v>
       </c>
-      <c r="E24" s="5" t="inlineStr"/>
+      <c r="E24" s="31" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="32" t="inlineStr">
         <is>
           <t>2026年03月</t>
         </is>
       </c>
-      <c r="B25" s="8" t="n">
+      <c r="B25" s="35" t="n">
         <v>8320</v>
       </c>
-      <c r="C25" s="8" t="n">
+      <c r="C25" s="25" t="n">
         <v>3339</v>
       </c>
-      <c r="D25" s="8" t="n">
+      <c r="D25" s="35" t="n">
         <v>11</v>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E25" s="33" t="inlineStr">
         <is>
           <t>好調</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="30" t="inlineStr">
         <is>
           <t>2026年04月</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n">
+      <c r="B26" s="34" t="n">
         <v>8370</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="23" t="n">
         <v>3672</v>
       </c>
-      <c r="D26" s="7" t="n">
+      <c r="D26" s="34" t="n">
         <v>11</v>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="31" t="inlineStr">
         <is>
           <t>好調</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="32" t="inlineStr">
         <is>
           <t>2026年05月</t>
         </is>
       </c>
-      <c r="B27" s="8" t="n">
+      <c r="B27" s="35" t="n">
         <v>16590</v>
       </c>
-      <c r="C27" s="8" t="n">
+      <c r="C27" s="25" t="n">
         <v>3968</v>
       </c>
-      <c r="D27" s="8" t="n">
+      <c r="D27" s="35" t="n">
         <v>11</v>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="33" t="inlineStr">
         <is>
           <t>好調</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="30" t="inlineStr">
         <is>
           <t>2026年06月</t>
         </is>
       </c>
-      <c r="B28" s="7" t="n">
+      <c r="B28" s="34" t="n">
         <v>900</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="23" t="n">
         <v>3257</v>
       </c>
-      <c r="D28" s="7" t="n">
+      <c r="D28" s="34" t="n">
         <v>11</v>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="31" t="inlineStr">
         <is>
           <t>まだ集計とちゅう（速報）</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="A29" s="32" t="inlineStr">
         <is>
           <t>▼ 今年の合計</t>
         </is>
       </c>
-      <c r="B29" s="12" t="n">
+      <c r="B29" s="35" t="n">
         <v>88412</v>
       </c>
-      <c r="C29" s="12" t="n">
+      <c r="C29" s="25" t="n">
         <v>37877</v>
       </c>
-      <c r="D29" s="12" t="n">
+      <c r="D29" s="35" t="n">
         <v>128</v>
       </c>
-      <c r="E29" s="11" t="inlineStr"/>
+      <c r="E29" s="33" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="30" t="n"/>
+      <c r="B30" s="31" t="n"/>
+      <c r="C30" s="18" t="n"/>
+      <c r="D30" s="31" t="n"/>
+      <c r="E30" s="31" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="32" t="n"/>
+      <c r="B31" s="33" t="n"/>
+      <c r="C31" s="21" t="n"/>
+      <c r="D31" s="33" t="n"/>
+      <c r="E31" s="33" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" s="30" t="inlineStr">
         <is>
           <t>③ ことばの説明（用語集）</t>
         </is>
       </c>
+      <c r="B32" s="31" t="n"/>
+      <c r="C32" s="18" t="n"/>
+      <c r="D32" s="31" t="n"/>
+      <c r="E32" s="31" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="32" t="inlineStr">
         <is>
           <t>ことば</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="33" t="inlineStr">
         <is>
           <t>かんたんな意味</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" s="21" t="inlineStr">
         <is>
           <t>たとえ</t>
         </is>
       </c>
+      <c r="D33" s="33" t="n"/>
+      <c r="E33" s="33" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="30" t="inlineStr">
         <is>
           <t>売上（うりあげ）</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="31" t="inlineStr">
         <is>
           <t>お客様から受け取るお金の総額</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="18" t="inlineStr">
         <is>
           <t>お店の『レジに入ったお金』全部</t>
         </is>
       </c>
+      <c r="D34" s="31" t="n"/>
+      <c r="E34" s="31" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="inlineStr">
+      <c r="A35" s="32" t="inlineStr">
         <is>
           <t>利益（りえき）</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B35" s="33" t="inlineStr">
         <is>
           <t>売上から、仕入れや手数料などの費用をひいて残るお金</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="21" t="inlineStr">
         <is>
           <t>『実際にもうかったお金』</t>
         </is>
       </c>
+      <c r="D35" s="33" t="n"/>
+      <c r="E35" s="33" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" s="30" t="inlineStr">
         <is>
           <t>粗利（あらり）</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B36" s="31" t="inlineStr">
         <is>
           <t>売上から仕入れ代だけをひいたお金（利益の手前）</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C36" s="18" t="inlineStr">
         <is>
           <t>費用をひく前の『ざっくり儲け』</t>
         </is>
       </c>
+      <c r="D36" s="31" t="n"/>
+      <c r="E36" s="31" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+      <c r="A37" s="32" t="inlineStr">
         <is>
           <t>件数（けんすう）</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B37" s="33" t="inlineStr">
         <is>
           <t>契約が決まった数</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C37" s="21" t="inlineStr">
         <is>
           <t>『何件売れたか』</t>
         </is>
       </c>
+      <c r="D37" s="33" t="n"/>
+      <c r="E37" s="33" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="30" t="inlineStr">
         <is>
           <t>利益率（りえきりつ）</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" s="31" t="inlineStr">
         <is>
           <t>売上のうち利益が占める割合（利益÷売上）</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C38" s="18" t="inlineStr">
         <is>
           <t>100円売って何円残るか</t>
         </is>
       </c>
+      <c r="D38" s="31" t="n"/>
+      <c r="E38" s="31" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="inlineStr">
+      <c r="A39" s="32" t="inlineStr">
         <is>
           <t>目標（もくひょう）</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B39" s="33" t="inlineStr">
         <is>
           <t>その年にめざす売上・利益の金額</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C39" s="21" t="inlineStr">
         <is>
           <t>ゴールの金額</t>
         </is>
       </c>
+      <c r="D39" s="33" t="n"/>
+      <c r="E39" s="33" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/経営管理/02_財務・会計/売上利益管理/初心者向け_売上利益シート.xlsx
+++ b/経営管理/02_財務・会計/売上利益管理/初心者向け_売上利益シート.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,8 +64,20 @@
       <color rgb="001A2433"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <color rgb="001A2433"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -102,8 +114,18 @@
         <fgColor rgb="00EEF3FA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0016293F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCE5F4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -159,11 +181,25 @@
         <color rgb="00C8A24B"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D7DEE8"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D7DEE8"/>
+      </right>
+      <top style="medium">
+        <color rgb="001F3A5F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D7DEE8"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -270,6 +306,52 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -647,16 +729,16 @@
     <col width="17.88" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t>🔰 かんたん売上利益シート（今年・第8期）</t>
         </is>
       </c>
-      <c r="B1" s="14" t="n"/>
-      <c r="C1" s="14" t="n"/>
-      <c r="D1" s="14" t="n"/>
-      <c r="E1" s="14" t="n"/>
+      <c r="B1" s="40" t="n"/>
+      <c r="C1" s="40" t="n"/>
+      <c r="D1" s="40" t="n"/>
+      <c r="E1" s="40" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -693,31 +775,31 @@
       <c r="E5" s="15" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>💰 売上（うりあげ）</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="42" t="inlineStr">
         <is>
           <t>8.8億円</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="43" t="inlineStr">
         <is>
           <t>お客様から受け取ったお金の合計</t>
         </is>
       </c>
-      <c r="D6" s="31" t="n"/>
-      <c r="E6" s="31" t="n"/>
+      <c r="D6" s="42" t="n"/>
+      <c r="E6" s="42" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="32" t="inlineStr">
+      <c r="A7" s="44" t="inlineStr">
         <is>
           <t>✨ 利益（りえき）</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="45" t="inlineStr">
         <is>
           <t>3.8億円</t>
         </is>
@@ -727,16 +809,16 @@
           <t>売上から費用をひいて、会社に残ったお金</t>
         </is>
       </c>
-      <c r="D7" s="33" t="n"/>
-      <c r="E7" s="33" t="n"/>
+      <c r="D7" s="45" t="n"/>
+      <c r="E7" s="45" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="A8" s="46" t="inlineStr">
         <is>
           <t>📝 契約の数</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="47" t="inlineStr">
         <is>
           <t>128件</t>
         </is>
@@ -746,16 +828,16 @@
           <t>今年これまでに決まった契約の件数</t>
         </is>
       </c>
-      <c r="D8" s="31" t="n"/>
-      <c r="E8" s="31" t="n"/>
+      <c r="D8" s="47" t="n"/>
+      <c r="E8" s="47" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="32" t="inlineStr">
+      <c r="A9" s="44" t="inlineStr">
         <is>
           <t>📊 1件あたりの利益</t>
         </is>
       </c>
-      <c r="B9" s="33" t="inlineStr">
+      <c r="B9" s="45" t="inlineStr">
         <is>
           <t>約296万円</t>
         </is>
@@ -765,16 +847,16 @@
           <t>契約1件で平均どれくらい儲かったか</t>
         </is>
       </c>
-      <c r="D9" s="33" t="n"/>
-      <c r="E9" s="33" t="n"/>
+      <c r="D9" s="45" t="n"/>
+      <c r="E9" s="45" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="A10" s="46" t="inlineStr">
         <is>
           <t>🎯 売上の目標</t>
         </is>
       </c>
-      <c r="B10" s="31" t="inlineStr">
+      <c r="B10" s="47" t="inlineStr">
         <is>
           <t>21億円</t>
         </is>
@@ -784,16 +866,16 @@
           <t>今年めざす売上</t>
         </is>
       </c>
-      <c r="D10" s="31" t="n"/>
-      <c r="E10" s="31" t="n"/>
+      <c r="D10" s="47" t="n"/>
+      <c r="E10" s="47" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="32" t="inlineStr">
+      <c r="A11" s="44" t="inlineStr">
         <is>
           <t xml:space="preserve">　→ 達成ぐあい</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="45" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
@@ -803,16 +885,16 @@
           <t>目標までどれくらい進んだか</t>
         </is>
       </c>
-      <c r="D11" s="33" t="n"/>
-      <c r="E11" s="33" t="n"/>
+      <c r="D11" s="45" t="n"/>
+      <c r="E11" s="45" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="30" t="inlineStr">
+      <c r="A12" s="46" t="inlineStr">
         <is>
           <t>🎯 利益の目標</t>
         </is>
       </c>
-      <c r="B12" s="31" t="inlineStr">
+      <c r="B12" s="47" t="inlineStr">
         <is>
           <t>4.8億円</t>
         </is>
@@ -822,16 +904,16 @@
           <t>今年めざす利益</t>
         </is>
       </c>
-      <c r="D12" s="31" t="n"/>
-      <c r="E12" s="31" t="n"/>
+      <c r="D12" s="47" t="n"/>
+      <c r="E12" s="47" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="32" t="inlineStr">
+      <c r="A13" s="44" t="inlineStr">
         <is>
           <t xml:space="preserve">　→ 達成ぐあい</t>
         </is>
       </c>
-      <c r="B13" s="33" t="inlineStr">
+      <c r="B13" s="45" t="inlineStr">
         <is>
           <t>79%</t>
         </is>
@@ -841,41 +923,41 @@
           <t>目標までどれくらい進んだか（あと少し！）</t>
         </is>
       </c>
-      <c r="D13" s="33" t="n"/>
-      <c r="E13" s="33" t="n"/>
+      <c r="D13" s="45" t="n"/>
+      <c r="E13" s="45" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="30" t="n"/>
-      <c r="B14" s="31" t="n"/>
+      <c r="A14" s="46" t="n"/>
+      <c r="B14" s="47" t="n"/>
       <c r="C14" s="18" t="n"/>
-      <c r="D14" s="31" t="n"/>
-      <c r="E14" s="31" t="n"/>
+      <c r="D14" s="47" t="n"/>
+      <c r="E14" s="47" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="32" t="n"/>
-      <c r="B15" s="33" t="n"/>
+      <c r="A15" s="44" t="n"/>
+      <c r="B15" s="45" t="n"/>
       <c r="C15" s="21" t="n"/>
-      <c r="D15" s="33" t="n"/>
-      <c r="E15" s="33" t="n"/>
+      <c r="D15" s="45" t="n"/>
+      <c r="E15" s="45" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="30" t="inlineStr">
+      <c r="A16" s="46" t="inlineStr">
         <is>
           <t>② 月ごとの売上と利益（万円）</t>
         </is>
       </c>
-      <c r="B16" s="31" t="n"/>
+      <c r="B16" s="47" t="n"/>
       <c r="C16" s="18" t="n"/>
-      <c r="D16" s="31" t="n"/>
-      <c r="E16" s="31" t="n"/>
+      <c r="D16" s="47" t="n"/>
+      <c r="E16" s="47" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="32" t="inlineStr">
+      <c r="A17" s="44" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="B17" s="33" t="inlineStr">
+      <c r="B17" s="45" t="inlineStr">
         <is>
           <t>売上（万円）</t>
         </is>
@@ -885,281 +967,281 @@
           <t>利益（万円）</t>
         </is>
       </c>
-      <c r="D17" s="33" t="inlineStr">
+      <c r="D17" s="45" t="inlineStr">
         <is>
           <t>契約数</t>
         </is>
       </c>
-      <c r="E17" s="33" t="inlineStr">
+      <c r="E17" s="45" t="inlineStr">
         <is>
           <t>ひとことメモ</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="30" t="inlineStr">
+      <c r="A18" s="46" t="inlineStr">
         <is>
           <t>2025年08月</t>
         </is>
       </c>
-      <c r="B18" s="34" t="n">
+      <c r="B18" s="48" t="n">
         <v>2650</v>
       </c>
       <c r="C18" s="23" t="n">
         <v>1995</v>
       </c>
-      <c r="D18" s="34" t="n">
+      <c r="D18" s="48" t="n">
         <v>10</v>
       </c>
-      <c r="E18" s="31" t="inlineStr"/>
+      <c r="E18" s="47" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="32" t="inlineStr">
+      <c r="A19" s="44" t="inlineStr">
         <is>
           <t>2025年09月</t>
         </is>
       </c>
-      <c r="B19" s="35" t="n">
+      <c r="B19" s="49" t="n">
         <v>12166</v>
       </c>
       <c r="C19" s="25" t="n">
         <v>3108</v>
       </c>
-      <c r="D19" s="35" t="n">
+      <c r="D19" s="49" t="n">
         <v>16</v>
       </c>
-      <c r="E19" s="33" t="inlineStr">
+      <c r="E19" s="45" t="inlineStr">
         <is>
           <t>好調</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="30" t="inlineStr">
+      <c r="A20" s="46" t="inlineStr">
         <is>
           <t>2025年10月</t>
         </is>
       </c>
-      <c r="B20" s="34" t="n">
+      <c r="B20" s="48" t="n">
         <v>8750</v>
       </c>
       <c r="C20" s="23" t="n">
         <v>1943</v>
       </c>
-      <c r="D20" s="34" t="n">
+      <c r="D20" s="48" t="n">
         <v>6</v>
       </c>
-      <c r="E20" s="31" t="inlineStr"/>
+      <c r="E20" s="47" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="32" t="inlineStr">
+      <c r="A21" s="44" t="inlineStr">
         <is>
           <t>2025年11月</t>
         </is>
       </c>
-      <c r="B21" s="35" t="n">
+      <c r="B21" s="49" t="n">
         <v>5846</v>
       </c>
       <c r="C21" s="25" t="n">
         <v>3279</v>
       </c>
-      <c r="D21" s="35" t="n">
+      <c r="D21" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="E21" s="33" t="inlineStr">
+      <c r="E21" s="45" t="inlineStr">
         <is>
           <t>好調</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="36" t="inlineStr">
+      <c r="A22" s="50" t="inlineStr">
         <is>
           <t>2025年12月</t>
         </is>
       </c>
-      <c r="B22" s="37" t="n">
+      <c r="B22" s="51" t="n">
         <v>18180</v>
       </c>
       <c r="C22" s="28" t="n">
         <v>7955</v>
       </c>
-      <c r="D22" s="37" t="n">
+      <c r="D22" s="51" t="n">
         <v>21</v>
       </c>
-      <c r="E22" s="38" t="inlineStr">
+      <c r="E22" s="52" t="inlineStr">
         <is>
           <t>⭐ いちばん利益が多い月！</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="32" t="inlineStr">
+      <c r="A23" s="44" t="inlineStr">
         <is>
           <t>2026年01月</t>
         </is>
       </c>
-      <c r="B23" s="35" t="n">
+      <c r="B23" s="49" t="n">
         <v>6640</v>
       </c>
       <c r="C23" s="25" t="n">
         <v>2367</v>
       </c>
-      <c r="D23" s="35" t="n">
+      <c r="D23" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="E23" s="33" t="inlineStr"/>
+      <c r="E23" s="45" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="30" t="inlineStr">
+      <c r="A24" s="46" t="inlineStr">
         <is>
           <t>2026年02月</t>
         </is>
       </c>
-      <c r="B24" s="34" t="n">
+      <c r="B24" s="48" t="n">
         <v>0</v>
       </c>
       <c r="C24" s="23" t="n">
         <v>2994</v>
       </c>
-      <c r="D24" s="34" t="n">
+      <c r="D24" s="48" t="n">
         <v>11</v>
       </c>
-      <c r="E24" s="31" t="inlineStr"/>
+      <c r="E24" s="47" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="32" t="inlineStr">
+      <c r="A25" s="44" t="inlineStr">
         <is>
           <t>2026年03月</t>
         </is>
       </c>
-      <c r="B25" s="35" t="n">
+      <c r="B25" s="49" t="n">
         <v>8320</v>
       </c>
       <c r="C25" s="25" t="n">
         <v>3339</v>
       </c>
-      <c r="D25" s="35" t="n">
+      <c r="D25" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="E25" s="33" t="inlineStr">
+      <c r="E25" s="45" t="inlineStr">
         <is>
           <t>好調</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="30" t="inlineStr">
+      <c r="A26" s="46" t="inlineStr">
         <is>
           <t>2026年04月</t>
         </is>
       </c>
-      <c r="B26" s="34" t="n">
+      <c r="B26" s="48" t="n">
         <v>8370</v>
       </c>
       <c r="C26" s="23" t="n">
         <v>3672</v>
       </c>
-      <c r="D26" s="34" t="n">
+      <c r="D26" s="48" t="n">
         <v>11</v>
       </c>
-      <c r="E26" s="31" t="inlineStr">
+      <c r="E26" s="47" t="inlineStr">
         <is>
           <t>好調</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="32" t="inlineStr">
+      <c r="A27" s="44" t="inlineStr">
         <is>
           <t>2026年05月</t>
         </is>
       </c>
-      <c r="B27" s="35" t="n">
+      <c r="B27" s="49" t="n">
         <v>16590</v>
       </c>
       <c r="C27" s="25" t="n">
         <v>3968</v>
       </c>
-      <c r="D27" s="35" t="n">
+      <c r="D27" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="E27" s="33" t="inlineStr">
+      <c r="E27" s="45" t="inlineStr">
         <is>
           <t>好調</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="30" t="inlineStr">
+      <c r="A28" s="46" t="inlineStr">
         <is>
           <t>2026年06月</t>
         </is>
       </c>
-      <c r="B28" s="34" t="n">
+      <c r="B28" s="48" t="n">
         <v>900</v>
       </c>
       <c r="C28" s="23" t="n">
         <v>3257</v>
       </c>
-      <c r="D28" s="34" t="n">
+      <c r="D28" s="48" t="n">
         <v>11</v>
       </c>
-      <c r="E28" s="31" t="inlineStr">
+      <c r="E28" s="47" t="inlineStr">
         <is>
           <t>まだ集計とちゅう（速報）</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="32" t="inlineStr">
+      <c r="A29" s="41" t="inlineStr">
         <is>
           <t>▼ 今年の合計</t>
         </is>
       </c>
-      <c r="B29" s="35" t="n">
+      <c r="B29" s="53" t="n">
         <v>88412</v>
       </c>
-      <c r="C29" s="25" t="n">
+      <c r="C29" s="54" t="n">
         <v>37877</v>
       </c>
-      <c r="D29" s="35" t="n">
+      <c r="D29" s="53" t="n">
         <v>128</v>
       </c>
-      <c r="E29" s="33" t="inlineStr"/>
+      <c r="E29" s="42" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="30" t="n"/>
-      <c r="B30" s="31" t="n"/>
+      <c r="A30" s="46" t="n"/>
+      <c r="B30" s="47" t="n"/>
       <c r="C30" s="18" t="n"/>
-      <c r="D30" s="31" t="n"/>
-      <c r="E30" s="31" t="n"/>
+      <c r="D30" s="47" t="n"/>
+      <c r="E30" s="47" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="32" t="n"/>
-      <c r="B31" s="33" t="n"/>
+      <c r="A31" s="44" t="n"/>
+      <c r="B31" s="45" t="n"/>
       <c r="C31" s="21" t="n"/>
-      <c r="D31" s="33" t="n"/>
-      <c r="E31" s="33" t="n"/>
+      <c r="D31" s="45" t="n"/>
+      <c r="E31" s="45" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="30" t="inlineStr">
+      <c r="A32" s="46" t="inlineStr">
         <is>
           <t>③ ことばの説明（用語集）</t>
         </is>
       </c>
-      <c r="B32" s="31" t="n"/>
+      <c r="B32" s="47" t="n"/>
       <c r="C32" s="18" t="n"/>
-      <c r="D32" s="31" t="n"/>
-      <c r="E32" s="31" t="n"/>
+      <c r="D32" s="47" t="n"/>
+      <c r="E32" s="47" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="32" t="inlineStr">
+      <c r="A33" s="44" t="inlineStr">
         <is>
           <t>ことば</t>
         </is>
       </c>
-      <c r="B33" s="33" t="inlineStr">
+      <c r="B33" s="45" t="inlineStr">
         <is>
           <t>かんたんな意味</t>
         </is>
@@ -1169,16 +1251,16 @@
           <t>たとえ</t>
         </is>
       </c>
-      <c r="D33" s="33" t="n"/>
-      <c r="E33" s="33" t="n"/>
+      <c r="D33" s="45" t="n"/>
+      <c r="E33" s="45" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="30" t="inlineStr">
+      <c r="A34" s="46" t="inlineStr">
         <is>
           <t>売上（うりあげ）</t>
         </is>
       </c>
-      <c r="B34" s="31" t="inlineStr">
+      <c r="B34" s="47" t="inlineStr">
         <is>
           <t>お客様から受け取るお金の総額</t>
         </is>
@@ -1188,16 +1270,16 @@
           <t>お店の『レジに入ったお金』全部</t>
         </is>
       </c>
-      <c r="D34" s="31" t="n"/>
-      <c r="E34" s="31" t="n"/>
+      <c r="D34" s="47" t="n"/>
+      <c r="E34" s="47" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="32" t="inlineStr">
+      <c r="A35" s="44" t="inlineStr">
         <is>
           <t>利益（りえき）</t>
         </is>
       </c>
-      <c r="B35" s="33" t="inlineStr">
+      <c r="B35" s="45" t="inlineStr">
         <is>
           <t>売上から、仕入れや手数料などの費用をひいて残るお金</t>
         </is>
@@ -1207,16 +1289,16 @@
           <t>『実際にもうかったお金』</t>
         </is>
       </c>
-      <c r="D35" s="33" t="n"/>
-      <c r="E35" s="33" t="n"/>
+      <c r="D35" s="45" t="n"/>
+      <c r="E35" s="45" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="30" t="inlineStr">
+      <c r="A36" s="46" t="inlineStr">
         <is>
           <t>粗利（あらり）</t>
         </is>
       </c>
-      <c r="B36" s="31" t="inlineStr">
+      <c r="B36" s="47" t="inlineStr">
         <is>
           <t>売上から仕入れ代だけをひいたお金（利益の手前）</t>
         </is>
@@ -1226,16 +1308,16 @@
           <t>費用をひく前の『ざっくり儲け』</t>
         </is>
       </c>
-      <c r="D36" s="31" t="n"/>
-      <c r="E36" s="31" t="n"/>
+      <c r="D36" s="47" t="n"/>
+      <c r="E36" s="47" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="32" t="inlineStr">
+      <c r="A37" s="44" t="inlineStr">
         <is>
           <t>件数（けんすう）</t>
         </is>
       </c>
-      <c r="B37" s="33" t="inlineStr">
+      <c r="B37" s="45" t="inlineStr">
         <is>
           <t>契約が決まった数</t>
         </is>
@@ -1245,16 +1327,16 @@
           <t>『何件売れたか』</t>
         </is>
       </c>
-      <c r="D37" s="33" t="n"/>
-      <c r="E37" s="33" t="n"/>
+      <c r="D37" s="45" t="n"/>
+      <c r="E37" s="45" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="30" t="inlineStr">
+      <c r="A38" s="46" t="inlineStr">
         <is>
           <t>利益率（りえきりつ）</t>
         </is>
       </c>
-      <c r="B38" s="31" t="inlineStr">
+      <c r="B38" s="47" t="inlineStr">
         <is>
           <t>売上のうち利益が占める割合（利益÷売上）</t>
         </is>
@@ -1264,16 +1346,16 @@
           <t>100円売って何円残るか</t>
         </is>
       </c>
-      <c r="D38" s="31" t="n"/>
-      <c r="E38" s="31" t="n"/>
+      <c r="D38" s="47" t="n"/>
+      <c r="E38" s="47" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="32" t="inlineStr">
+      <c r="A39" s="44" t="inlineStr">
         <is>
           <t>目標（もくひょう）</t>
         </is>
       </c>
-      <c r="B39" s="33" t="inlineStr">
+      <c r="B39" s="45" t="inlineStr">
         <is>
           <t>その年にめざす売上・利益の金額</t>
         </is>
@@ -1283,8 +1365,8 @@
           <t>ゴールの金額</t>
         </is>
       </c>
-      <c r="D39" s="33" t="n"/>
-      <c r="E39" s="33" t="n"/>
+      <c r="D39" s="45" t="n"/>
+      <c r="E39" s="45" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
